--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFB5823F-684C-41C0-B96F-02A9AB51FEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15A87EC9-0DA3-4FF9-A63D-D0412638E70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F72F2FCA-B7BA-4D95-A431-E4D7F995115D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{C9DDC34A-DB59-45B3-BBAA-3CCFB5C4785A}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
   <si>
     <r>
       <t>ICT</t>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>27</t>
     </r>
     <r>
       <rPr>
@@ -247,7 +247,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>における支払い管理、購入履歴、購読管理、プラン選択に関する機能を含んでいます。</t>
+      <t>上で支払い管理、購入処理、注文履歴、サブスクリプション管理とプラン選択を扱う機能群です。</t>
     </r>
   </si>
   <si>
@@ -444,8 +444,11 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
-    </r>
+      <t>評価不要</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>ヒョウカフヨウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -457,20 +460,26 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
+      <t>条を用いているため評価の対象外である。</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -483,7 +492,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
     </r>
   </si>
   <si>
@@ -496,7 +505,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた聴力での使用（難聴）</t>
+      <t>聴力なしでの使用（全ろう）</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -509,7 +518,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
     </r>
   </si>
   <si>
@@ -522,7 +531,46 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>限られた聴力での使用（難聴）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>発話能力なしでの使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2227,14 +2275,14 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1730375</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>49741</xdr:rowOff>
+      <xdr:rowOff>52916</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB2F85E5-DE40-4E07-8ECC-BC4D6D90EB2C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{611C8E83-B86A-4647-99FB-40844AC7A7F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2257,7 +2305,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6543675" y="552450"/>
-          <a:ext cx="2647950" cy="2653241"/>
+          <a:ext cx="2647950" cy="2656416"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2585,7 +2633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71ADCAE-15A2-4C4D-AB68-C8E9C8458480}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CEFA91F-845E-4345-9B38-43EBB5257AC4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2885,7 +2933,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>24</v>
       </c>
@@ -2894,30 +2942,30 @@
       <c r="D22" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
@@ -2934,7 +2982,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2947,7 +2995,7 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
@@ -2964,7 +3012,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2977,12 +3025,12 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>20</v>
@@ -2994,7 +3042,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -3007,7 +3055,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -3024,7 +3072,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3037,7 +3085,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3050,7 +3098,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3063,15 +3111,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3080,7 +3128,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3121,15 +3169,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3138,7 +3186,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3162,7 +3210,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3192,15 +3240,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3209,7 +3257,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3233,10 +3281,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3259,7 +3307,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3399,7 +3447,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{4F05D006-D000-4A19-A9DA-9E954F57E046}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{C066329B-2E2D-45B7-AC0E-6BBB92814F60}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3408,7 +3456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7FA0DC-57D6-4570-9682-6F53DA78BA47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3C4728-6E77-4A52-9928-26E2C1136F46}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3421,43 +3469,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3465,36 +3513,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3502,10 +3550,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3523,14 +3571,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3546,15 +3594,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3569,15 +3617,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3592,17 +3640,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3615,10 +3663,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3626,7 +3674,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3638,10 +3686,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3650,7 +3698,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3661,10 +3709,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3674,10 +3722,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3686,10 +3734,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3699,10 +3747,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3711,10 +3759,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3732,17 +3780,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3757,10 +3805,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3778,10 +3826,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3796,17 +3844,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3819,17 +3867,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3842,20 +3890,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3867,20 +3915,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3892,17 +3940,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3918,10 +3966,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3929,7 +3977,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3938,23 +3986,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3963,23 +4011,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3991,15 +4039,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4014,15 +4062,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4037,27 +4085,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4066,10 +4114,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4087,29 +4135,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4118,10 +4166,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4139,17 +4187,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4164,10 +4212,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4185,30 +4233,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4216,10 +4264,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4237,31 +4285,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4270,10 +4318,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4291,15 +4339,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4314,14 +4362,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4337,10 +4385,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4350,10 +4398,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4362,27 +4410,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4391,10 +4439,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4404,10 +4452,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4416,14 +4464,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4439,10 +4487,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4452,10 +4500,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4464,10 +4512,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4477,10 +4525,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4489,10 +4537,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4510,10 +4558,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4531,10 +4579,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4552,14 +4600,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4575,10 +4623,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4596,15 +4644,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4619,10 +4667,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4640,20 +4688,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4665,10 +4713,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4686,29 +4734,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4717,10 +4765,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4738,10 +4786,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4749,7 +4797,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4761,10 +4809,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4772,7 +4820,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4784,10 +4832,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4795,7 +4843,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4807,10 +4855,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4828,24 +4876,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4857,17 +4905,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4880,20 +4928,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4905,10 +4953,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4926,14 +4974,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4949,10 +4997,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4970,22 +5018,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4997,10 +5045,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5018,31 +5066,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5051,10 +5099,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5072,29 +5120,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5103,14 +5151,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5118,10 +5166,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5130,43 +5178,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5176,22 +5224,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5201,22 +5249,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5226,32 +5274,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5260,23 +5308,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5285,26 +5333,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5312,23 +5360,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5340,31 +5388,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5373,10 +5421,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5394,15 +5442,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5417,14 +5465,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5432,10 +5480,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5444,22 +5492,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5471,24 +5519,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5500,10 +5548,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5521,24 +5569,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5547,25 +5595,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5574,20 +5622,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5602,24 +5650,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5631,24 +5679,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15A87EC9-0DA3-4FF9-A63D-D0412638E70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{183F4014-083E-48A7-AFAF-7BC8F3FC1BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{C9DDC34A-DB59-45B3-BBAA-3CCFB5C4785A}"/>
+    <workbookView xWindow="2280" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{69CC4D23-890B-4DCE-B285-1CE2B8C1F9B1}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>27</t>
+      <t>17</t>
     </r>
     <r>
       <rPr>
@@ -2282,7 +2282,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{611C8E83-B86A-4647-99FB-40844AC7A7F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA626D2B-8E2F-479E-9369-B37DCF3A08F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2633,7 +2633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CEFA91F-845E-4345-9B38-43EBB5257AC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D17CAC4-711C-444B-B846-C8F90794B0BB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3447,7 +3447,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{C066329B-2E2D-45B7-AC0E-6BBB92814F60}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{A6E9C6FA-392C-4DC1-8C1B-1721772F7EAC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3456,7 +3456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3C4728-6E77-4A52-9928-26E2C1136F46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6001321D-1271-4085-84E0-4E2343871537}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{183F4014-083E-48A7-AFAF-7BC8F3FC1BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE9D2C7-8CB5-4744-B427-94555C4F9A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{69CC4D23-890B-4DCE-B285-1CE2B8C1F9B1}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="11960" windowHeight="13930" xr2:uid="{1E0F8B77-C2D2-487D-8CCD-83FD25325B6B}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
   <si>
     <r>
       <t>ICT</t>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>27</t>
     </r>
     <r>
       <rPr>
@@ -572,6 +572,9 @@
       </rPr>
       <t>対応している</t>
     </r>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -583,72 +586,98 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた器用さ又は力での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた手の届く範囲での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>光の点滅による影響の最小化（光感受性発作）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2275,14 +2304,14 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1730375</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>52916</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA626D2B-8E2F-479E-9369-B37DCF3A08F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4612C0-9678-4505-B9F5-A9B385B360A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2305,7 +2334,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6543675" y="552450"/>
-          <a:ext cx="2647950" cy="2656416"/>
+          <a:ext cx="2647950" cy="2641600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2633,7 +2662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D17CAC4-711C-444B-B846-C8F90794B0BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2615FF87-8231-4C5F-ACBE-017C92701DE6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2933,7 +2962,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>24</v>
       </c>
@@ -3032,30 +3061,30 @@
       <c r="D28" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
+      <c r="E28" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
       <c r="D29" s="47"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -3072,7 +3101,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3085,7 +3114,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3098,7 +3127,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3111,15 +3140,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3128,7 +3157,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3169,15 +3198,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3186,7 +3215,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3210,7 +3239,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3240,15 +3269,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3257,7 +3286,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3281,10 +3310,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3307,7 +3336,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3447,7 +3476,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{A6E9C6FA-392C-4DC1-8C1B-1721772F7EAC}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{232101C3-F2B7-4E81-924F-CA1F5D4C98C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3456,7 +3485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6001321D-1271-4085-84E0-4E2343871537}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445A473B-A424-41E5-9AC8-9D98E6DA98B6}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3469,43 +3498,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3513,36 +3542,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3550,10 +3579,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3571,14 +3600,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3594,15 +3623,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3617,15 +3646,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3640,17 +3669,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3663,10 +3692,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3674,7 +3703,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3686,10 +3715,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3698,7 +3727,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3709,10 +3738,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3722,10 +3751,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3734,10 +3763,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3747,10 +3776,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3759,10 +3788,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3780,17 +3809,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3805,10 +3834,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3826,10 +3855,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3844,17 +3873,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3867,17 +3896,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3890,20 +3919,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3915,20 +3944,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3940,17 +3969,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3966,10 +3995,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3977,7 +4006,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3986,23 +4015,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -4011,23 +4040,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4039,15 +4068,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4062,15 +4091,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4085,27 +4114,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4114,10 +4143,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4135,29 +4164,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4166,10 +4195,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4187,17 +4216,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4212,10 +4241,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4233,30 +4262,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4264,10 +4293,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4285,31 +4314,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4318,10 +4347,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4339,15 +4368,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4362,14 +4391,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4385,10 +4414,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4398,10 +4427,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4410,27 +4439,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4439,10 +4468,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4452,10 +4481,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4464,14 +4493,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4487,10 +4516,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4500,10 +4529,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4512,10 +4541,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4525,10 +4554,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4537,10 +4566,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4558,10 +4587,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4579,10 +4608,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4600,14 +4629,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4623,10 +4652,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4644,15 +4673,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4667,10 +4696,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4688,20 +4717,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4713,10 +4742,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4734,29 +4763,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4765,10 +4794,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4786,10 +4815,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4797,7 +4826,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4809,10 +4838,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4820,7 +4849,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4832,10 +4861,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4843,7 +4872,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4855,10 +4884,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4876,24 +4905,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4905,17 +4934,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4928,20 +4957,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4953,10 +4982,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4974,14 +5003,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4997,10 +5026,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -5018,22 +5047,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5045,10 +5074,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5066,31 +5095,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5099,10 +5128,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5120,29 +5149,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5151,14 +5180,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5166,10 +5195,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5178,43 +5207,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5224,22 +5253,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5249,22 +5278,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5274,32 +5303,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5308,23 +5337,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5333,26 +5362,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5360,23 +5389,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5388,31 +5417,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5421,10 +5450,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5442,15 +5471,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5465,14 +5494,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5480,10 +5509,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5492,22 +5521,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5519,24 +5548,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5548,10 +5577,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5569,24 +5598,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5595,25 +5624,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5622,20 +5651,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5650,24 +5679,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5679,24 +5708,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE9D2C7-8CB5-4744-B427-94555C4F9A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F473B8E3-0918-4ACA-B693-07467FABF2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="11960" windowHeight="13930" xr2:uid="{1E0F8B77-C2D2-487D-8CCD-83FD25325B6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E7ECE0CB-08AA-4B49-AE93-5F758EAA28D0}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -2311,7 +2311,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4612C0-9678-4505-B9F5-A9B385B360A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9AB0D6-2151-43E9-9101-5ACF88A637F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2662,7 +2662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2615FF87-8231-4C5F-ACBE-017C92701DE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5E4277-BDC3-4C1B-AB14-0192C6B16460}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3476,7 +3476,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{232101C3-F2B7-4E81-924F-CA1F5D4C98C4}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{6A146BA4-AFEE-47EF-9771-E6AAA874063C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3485,7 +3485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445A473B-A424-41E5-9AC8-9D98E6DA98B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA2A69B-473F-4A14-9635-02E50C51BC59}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F473B8E3-0918-4ACA-B693-07467FABF2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06475D6B-B690-4156-BF94-0E532FD85C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E7ECE0CB-08AA-4B49-AE93-5F758EAA28D0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{3CB9CC6D-C741-47C6-98D5-30F3BE6C98C8}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>27</t>
+      <t>17</t>
     </r>
     <r>
       <rPr>
@@ -2311,7 +2311,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9AB0D6-2151-43E9-9101-5ACF88A637F2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A5E6AA-535D-4860-929C-98D80FD30F8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2662,7 +2662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5E4277-BDC3-4C1B-AB14-0192C6B16460}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F1EAFA-FA57-4294-AB6A-90358001CE13}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3476,7 +3476,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{6A146BA4-AFEE-47EF-9771-E6AAA874063C}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{4A0EA914-2A4C-4C27-8BDA-D4B630E1DD0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3485,7 +3485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA2A69B-473F-4A14-9635-02E50C51BC59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB1980-80E3-491A-A751-104387E74528}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06475D6B-B690-4156-BF94-0E532FD85C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0482BDD3-7B30-4FAA-AA2F-467AC189E19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{3CB9CC6D-C741-47C6-98D5-30F3BE6C98C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5696CAB4-F63A-4F7D-A331-BCFFCCEBD5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -37,6 +37,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
   <si>
@@ -111,7 +133,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>27</t>
     </r>
     <r>
       <rPr>
@@ -188,7 +210,6 @@
   </si>
   <si>
     <t>Xbox Console OS - Non-store e-commerce experiences</t>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -1696,7 +1717,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2291,59 +2312,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1730375</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A5E6AA-535D-4860-929C-98D80FD30F8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6543675" y="552450"/>
-          <a:ext cx="2647950" cy="2641600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2662,8 +2692,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F1EAFA-FA57-4294-AB6A-90358001CE13}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49BDBD7-21EE-456D-9EF1-B7BE16CE587E}">
+  <sheetPr codeName="Sheet270">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2729,7 +2759,9 @@
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="H4" s="12"/>
       <c r="I4" s="13"/>
     </row>
@@ -3476,16 +3508,15 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{4A0EA914-2A4C-4C27-8BDA-D4B630E1DD0E}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{54F148E9-6503-4B69-B4EB-6AD04ECC1B89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB1980-80E3-491A-A751-104387E74528}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212CD172-5F84-46C5-9A57-EFF33AB306E7}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0482BDD3-7B30-4FAA-AA2F-467AC189E19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D99561B-FE6C-429B-ACE5-E213225CF970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5696CAB4-F63A-4F7D-A331-BCFFCCEBD5CB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{DB3920EA-3314-44D5-852A-7B2D31306E98}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -60,815 +60,196 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービスのアクセシビリティ自己評価様式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>作成日：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品画像</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>企業・団体名</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日本マイクロソフト株式会社</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+  <si>
+    <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
+  </si>
+  <si>
+    <t>作成日：2026年4月17日</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品画像</t>
+  </si>
+  <si>
+    <t>企業・団体名</t>
+  </si>
+  <si>
+    <t>日本マイクロソフト株式会社</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス名称</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ICT機器・サービス名称</t>
   </si>
   <si>
     <t>Xbox Console OS - Non-store e-commerce experiences</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>型番</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Xbox Console OS - Non-store e-commerce experiences</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Xbox OS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>上で支払い管理、購入処理、注文履歴、サブスクリプション管理とプラン選択を扱う機能群です。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>問合せ先</t>
-    </r>
+    <t>型番</t>
+  </si>
+  <si>
+    <t>ICT機器・サービス概要</t>
+  </si>
+  <si>
+    <t>Xbox Console OS - Non-store e-commerce experiencesは、Xbox OS上で支払い管理、購入処理、注文履歴、サブスクリプション管理とプラン選択を扱う機能群です。</t>
+  </si>
+  <si>
+    <t>問合せ先</t>
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ウェブサイト</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウェブサイトURL</t>
   </si>
   <si>
     <t>https://www.xbox.com/ja-JP/consoles</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機能性能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配慮対象アクセス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価結果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価不要</t>
-    </r>
+    <t>機能性能</t>
+  </si>
+  <si>
+    <t>配慮対象アクセス</t>
+  </si>
+  <si>
+    <t>評価結果</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>視力なしでの使用（全盲）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>色知覚なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>聴力なしでの使用（全ろう）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた聴力での使用（難聴）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+  </si>
+  <si>
+    <t>発話能力なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた器用さ又は力での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた手の届く範囲での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>光の点滅による影響の最小化（光感受性発作）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>免責事項</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+  </si>
+  <si>
+    <t>プライバシー</t>
+  </si>
+  <si>
+    <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>サポート対応　概要</t>
+  </si>
+  <si>
+    <t>ドキュメントとサポートサービス</t>
+  </si>
+  <si>
+    <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、FAX等）が提供されているか。</t>
+  </si>
+  <si>
+    <t>用いた技術基準</t>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>免責事項</t>
   </si>
   <si>
     <t>章・項・節</t>
@@ -881,18 +262,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -902,84 +283,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -989,11 +334,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -1003,22 +348,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -1028,22 +373,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -1053,11 +398,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -1067,138 +412,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -1211,88 +556,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -1302,32 +647,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -1337,88 +682,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -1428,28 +773,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -1459,164 +804,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -1626,7 +971,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1648,13 +993,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1667,26 +1005,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1696,13 +1021,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1716,35 +1056,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="36"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="10.5"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2081,184 +1404,184 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2282,16 +1605,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2692,230 +2015,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49BDBD7-21EE-456D-9EF1-B7BE16CE587E}">
-  <sheetPr codeName="Sheet270">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D3A0E9-2E5B-4D67-9B10-7F407EDB30CD}">
+  <sheetPr codeName="Sheet373">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="3"/>
-    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="3"/>
+    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="2"/>
+    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="11" t="e" vm="1">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="2"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -3259,28 +2582,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3330,15 +2653,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3357,11 +2680,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3506,9 +2829,9 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{54F148E9-6503-4B69-B4EB-6AD04ECC1B89}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{A5820E5A-714E-436C-85DD-F875E57B5C6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3516,7 +2839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212CD172-5F84-46C5-9A57-EFF33AB306E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAE1400-5F6F-4147-ADE7-B20A1D5155E4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3541,31 +2864,31 @@
         <v>55</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3573,36 +2896,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3610,10 +2933,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3631,14 +2954,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3654,15 +2977,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3677,15 +3000,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3700,17 +3023,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3723,10 +3046,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3734,7 +3057,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3746,10 +3069,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3758,7 +3081,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3769,10 +3092,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3782,10 +3105,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3794,10 +3117,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3807,10 +3130,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3819,10 +3142,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3840,17 +3163,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3865,10 +3188,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3886,10 +3209,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3904,17 +3227,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3927,17 +3250,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3950,20 +3273,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3975,20 +3298,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -4000,17 +3323,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -4026,10 +3349,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -4037,7 +3360,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -4046,23 +3369,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -4071,23 +3394,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4099,15 +3422,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4122,15 +3445,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4145,27 +3468,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4174,10 +3497,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4195,29 +3518,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4226,10 +3549,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4247,17 +3570,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4272,10 +3595,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4293,30 +3616,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4324,10 +3647,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4345,31 +3668,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4378,10 +3701,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4399,15 +3722,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4422,14 +3745,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4445,10 +3768,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4458,10 +3781,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4470,27 +3793,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4499,10 +3822,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4512,10 +3835,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4524,14 +3847,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4547,10 +3870,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4560,10 +3883,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4572,10 +3895,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4585,10 +3908,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4597,10 +3920,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4618,10 +3941,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4639,10 +3962,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4660,14 +3983,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4683,10 +4006,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4704,15 +4027,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4727,10 +4050,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4748,20 +4071,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4773,10 +4096,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4794,29 +4117,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4825,10 +4148,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4846,10 +4169,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4857,7 +4180,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4869,10 +4192,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4880,7 +4203,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4892,10 +4215,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4903,7 +4226,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4915,10 +4238,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4936,24 +4259,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4965,17 +4288,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4988,20 +4311,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -5013,10 +4336,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -5034,14 +4357,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -5057,10 +4380,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -5078,22 +4401,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5105,10 +4428,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5126,31 +4449,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5159,10 +4482,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5180,29 +4503,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5211,14 +4534,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5226,10 +4549,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5238,43 +4561,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5284,22 +4607,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5309,22 +4632,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5334,32 +4657,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5368,23 +4691,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5393,26 +4716,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5420,23 +4743,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5448,31 +4771,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5481,10 +4804,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5502,15 +4825,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5525,14 +4848,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5540,10 +4863,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5552,22 +4875,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5579,24 +4902,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5608,10 +4931,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5629,24 +4952,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5655,25 +4978,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5682,20 +5005,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5710,24 +5033,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5739,24 +5062,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5930,7 +5253,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D99561B-FE6C-429B-ACE5-E213225CF970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{360B4F5F-BDCA-4FBD-8D4A-B85D995D6E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{DB3920EA-3314-44D5-852A-7B2D31306E98}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{EC72A67D-783B-4832-9A79-CCCA9CE7C7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -37,35 +37,13 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
   <si>
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年4月17日</t>
+    <t>作成日：2026年4月27日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1635,68 +1613,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1670050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1" descr="XBOXのロゴ画像">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8660C75-AD92-4590-9518-9D6E0429885C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6527800" y="536575"/>
+          <a:ext cx="2603500" cy="2597150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2015,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D3A0E9-2E5B-4D67-9B10-7F407EDB30CD}">
-  <sheetPr codeName="Sheet373">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B820EC61-2299-4E31-8771-87BF60FE0CAE}">
+  <sheetPr codeName="Sheet333">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2082,9 +2051,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="10" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
     </row>
@@ -2831,15 +2798,16 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{A5820E5A-714E-436C-85DD-F875E57B5C6F}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{8892A13D-4637-4F90-BD6A-537FAE8A41F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAE1400-5F6F-4147-ADE7-B20A1D5155E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6282076E-6178-4306-9386-E34B8210BF94}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
+++ b/file/Xbox_Console_OS_-_Non-store_e-commerce_experiences_VPATJ17361.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{360B4F5F-BDCA-4FBD-8D4A-B85D995D6E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2486BC11-8BA1-4E12-9E3D-E3AA74485C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{EC72A67D-783B-4832-9A79-CCCA9CE7C7B6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F1FA77D3-669A-4FE7-BB8C-C30C62B53714}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年4月27日</t>
+    <t>作成日：2026年4月17日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1633,7 +1633,7 @@
         <xdr:cNvPr id="2" name="図 1" descr="XBOXのロゴ画像">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8660C75-AD92-4590-9518-9D6E0429885C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D6907F-D037-42E0-9D68-AFC4D8775C8B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1984,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B820EC61-2299-4E31-8771-87BF60FE0CAE}">
-  <sheetPr codeName="Sheet333">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A97A1FF-68E2-40F9-8A34-99E4CD44BC21}">
+  <sheetPr codeName="Sheet414">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2798,7 +2798,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{8892A13D-4637-4F90-BD6A-537FAE8A41F4}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{9E5AE75B-5445-4EDC-B267-4D0EE0555BFA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2807,7 +2807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6282076E-6178-4306-9386-E34B8210BF94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863F6661-52D9-4FC7-9FD8-A036593E8401}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
